--- a/docs/assets/infraestructura/s2-e3-inventario-final-activos.xlsx
+++ b/docs/assets/infraestructura/s2-e3-inventario-final-activos.xlsx
@@ -495,7 +495,7 @@
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="38.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="44.83203125" customWidth="1"/>
+    <col min="6" max="6" width="37.83203125" customWidth="1"/>
     <col min="7" max="7" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -654,10 +654,10 @@
         <v>Alta</v>
       </c>
       <c r="F7" t="str">
-        <v>Operativo (versión corregida sin publicar)</v>
+        <v>Operativo (publicada 2026-10-24)</v>
       </c>
       <c r="G7" t="str">
-        <v>firestore.rules y 19 pruebas; ruleset publicado el 22-jun-2026</v>
+        <v>firestore.rules y 19 pruebas; versión corregida publicada el 2026-10-24 (reemplazó la del 22-jun-2026)</v>
       </c>
     </row>
     <row r="8">
@@ -700,10 +700,10 @@
         <v>Alta</v>
       </c>
       <c r="F9" t="str">
-        <v>Operativo (con hallazgo NC-03)</v>
+        <v>Operativo (clave rotada 2026-10-24)</v>
       </c>
       <c r="G9" t="str">
-        <v>db-crear-usuarios.js lee contraseñas del entorno; hallazgo H-03</v>
+        <v>db-crear-usuarios.js lee contraseñas del entorno; clave de servicio rotada (H-03 corregido)</v>
       </c>
     </row>
     <row r="10">
@@ -726,7 +726,7 @@
         <v>Parcial (solo MySQL)</v>
       </c>
       <c r="G10" t="str">
-        <v>backup.js y restore.js; REC-01 y REC-02</v>
+        <v>backup.js y restore.js; REC-01, REC-02 y REC-05 (base real)</v>
       </c>
     </row>
     <row r="11">

--- a/docs/assets/infraestructura/s2-e3-inventario-final-activos.xlsx
+++ b/docs/assets/infraestructura/s2-e3-inventario-final-activos.xlsx
@@ -493,7 +493,7 @@
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="37.83203125" customWidth="1"/>
     <col min="7" max="7" width="60.83203125" customWidth="1"/>
@@ -680,7 +680,7 @@
         <v>Operativo</v>
       </c>
       <c r="G8" t="str">
-        <v>.github/workflows/ci.yml (6 trabajos); 90 pruebas</v>
+        <v>.github/workflows/ci.yml (6 trabajos); 99 pruebas</v>
       </c>
     </row>
     <row r="9">
@@ -717,7 +717,7 @@
         <v>Responsable de respaldos</v>
       </c>
       <c r="D10" t="str">
-        <v>PC local, VPS, PBS y disco externo</v>
+        <v>VPS (respaldo diario de MySQL), PC (copia semanal), PBS y disco externo</v>
       </c>
       <c r="E10" t="str">
         <v>Crítica</v>
@@ -726,7 +726,7 @@
         <v>Parcial (solo MySQL)</v>
       </c>
       <c r="G10" t="str">
-        <v>backup.js y restore.js; REC-01, REC-02 y REC-05 (base real)</v>
+        <v>Temporizador academia-respaldo (diario, 03:00); REC-01, REC-02, REC-05, REC-13 y REC-14</v>
       </c>
     </row>
     <row r="11">
@@ -763,7 +763,7 @@
         <v>Responsable de seguridad</v>
       </c>
       <c r="D12" t="str">
-        <v>VPS, PC local y VM-SIEM01</v>
+        <v>VPS y VM-SIEM01</v>
       </c>
       <c r="E12" t="str">
         <v>Alta</v>
@@ -772,7 +772,7 @@
         <v>Parcial (sin centralizar)</v>
       </c>
       <c r="G12" t="str">
-        <v>morgan en server/src/index.ts; registros de Nginx en el VPS</v>
+        <v>morgan en server/src/index.ts, con sus registros en PM2 del VPS; registros de Nginx en el VPS</v>
       </c>
     </row>
     <row r="13">
@@ -878,16 +878,16 @@
         <v>Líder técnico</v>
       </c>
       <c r="D17" t="str">
-        <v>PC local (destino: VM-APP01)</v>
+        <v>VPS del colegio, usuario academia (destino de diseño: VM-APP01)</v>
       </c>
       <c r="E17" t="str">
         <v>Alta</v>
       </c>
       <c r="F17" t="str">
-        <v>Transitorio</v>
+        <v>Operativo (VPS desde 2026-10-24)</v>
       </c>
       <c r="G17" t="str">
-        <v>helmet, CORS y morgan en server/src/index.ts; 18 pruebas</v>
+        <v>helmet, CORS y morgan en server/src/index.ts; 27 pruebas; HTTPS en api-academia y analitica-academia; prueba de punta a punta del 2026-10-24</v>
       </c>
     </row>
     <row r="18">
@@ -901,16 +901,16 @@
         <v>Líder técnico</v>
       </c>
       <c r="D18" t="str">
-        <v>PC local (destino: VM-APP01)</v>
+        <v>VPS del colegio (destino de diseño: VM-APP01)</v>
       </c>
       <c r="E18" t="str">
         <v>Alta</v>
       </c>
       <c r="F18" t="str">
-        <v>Transitorio</v>
+        <v>Operativo (VPS desde 2026-10-24)</v>
       </c>
       <c r="G18" t="str">
-        <v>Roles de 04_seguridad.sql; 19 pruebas SQL</v>
+        <v>Roles de 04_seguridad.sql; 19 pruebas SQL; migración 05; respaldo diario</v>
       </c>
     </row>
     <row r="19">
@@ -956,7 +956,7 @@
         <v>Operativo</v>
       </c>
       <c r="G20" t="str">
-        <v>Manual del VPS; PR-01 a PR-09</v>
+        <v>Manual del VPS; PR-01 a PR-09; desde el 2026-10-24 aloja también la capa de la academia (usuario academia)</v>
       </c>
     </row>
     <row r="21">
@@ -964,7 +964,7 @@
         <v>ACT-20</v>
       </c>
       <c r="B21" t="str">
-        <v>PC local con PM2 (servicios transitorios)</v>
+        <v>PC local con PM2 (servicios anteriores de la capa)</v>
       </c>
       <c r="C21" t="str">
         <v>Dirección de la academia</v>
@@ -976,10 +976,10 @@
         <v>Alta</v>
       </c>
       <c r="F21" t="str">
-        <v>Transitorio</v>
+        <v>Retirado (2026-10-24)</v>
       </c>
       <c r="G21" t="str">
-        <v>npm run pm2:start en server/package.json</v>
+        <v>pm2 stop y pm2 save el 2026-10-24; Laragon queda para pruebas de restauración (REC-14)</v>
       </c>
     </row>
     <row r="22">
